--- a/downloads/Literature_Matrix_Working_Copy_with_Summary.xlsx
+++ b/downloads/Literature_Matrix_Working_Copy_with_Summary.xlsx
@@ -2236,7 +2236,7 @@
     <t xml:space="preserve">Compared with matched controls, participants improved sleep consistency, resting heart rate and HRV. Better sleep consistency partly explained the gains in fitness and parasympathetic activity.</t>
   </si>
   <si>
-    <t xml:space="preserve">Not randomised; authors work for WHOOP; healthy users, no burnout measure.</t>
+    <t xml:space="preserve">Not randomised; lead author works for WHOOP; healthy users, no burnout measure.</t>
   </si>
   <si>
     <t xml:space="preserve">Links sleep consistency with HRV in a very large wearable sample.</t>
